--- a/outputs/monitor_xlsx/20260129.xlsx
+++ b/outputs/monitor_xlsx/20260129.xlsx
@@ -481,6 +481,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -823,6 +824,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -878,6 +880,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -999,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V25"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1107,40 +1110,35 @@
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1193,12 +1191,7 @@
       <c r="N4" t="n">
         <v>-0.79</v>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1239,12 +1232,7 @@
       <c r="M5" t="n">
         <v>-22201</v>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1297,12 +1285,7 @@
       <c r="N6" t="n">
         <v>21.14</v>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1355,12 +1338,7 @@
       <c r="N7" t="n">
         <v>23.04</v>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1413,12 +1391,7 @@
       <c r="N8" t="n">
         <v>21.82</v>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1471,12 +1444,7 @@
       <c r="N9" t="n">
         <v>23.09</v>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1529,12 +1497,7 @@
       <c r="N10" t="n">
         <v>37.67</v>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1587,12 +1550,7 @@
       <c r="N11" t="n">
         <v>24.4</v>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1645,12 +1603,7 @@
       <c r="N12" t="n">
         <v>19.49</v>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1703,12 +1656,7 @@
       <c r="N13" t="n">
         <v>19.61</v>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1761,12 +1709,7 @@
       <c r="N14" t="n">
         <v>55.09</v>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1819,12 +1762,7 @@
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1877,12 +1815,7 @@
       <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1935,12 +1868,7 @@
       <c r="N17" t="n">
         <v>0</v>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1993,12 +1921,7 @@
       <c r="N18" t="n">
         <v>0</v>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2051,12 +1974,7 @@
       <c r="N19" t="n">
         <v>23.88</v>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2109,11 +2027,6 @@
       <c r="N20" t="n">
         <v>-7.65</v>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2162,11 +2075,6 @@
       <c r="N21" t="n">
         <v>5.03</v>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2215,11 +2123,6 @@
       <c r="N22" t="n">
         <v>-7.88</v>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2268,11 +2171,6 @@
       <c r="N23" t="n">
         <v>-0.97</v>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2321,11 +2219,6 @@
       <c r="N24" t="n">
         <v>0</v>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2373,11 +2266,6 @@
       </c>
       <c r="N25" t="n">
         <v>8.75</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260129.xlsx
+++ b/outputs/monitor_xlsx/20260129.xlsx
@@ -481,7 +481,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -824,7 +823,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -880,7 +878,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1002,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1152,44 +1149,49 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+          <t>元大台灣50</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
         <v>73.75</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="E4" s="6" t="n">
         <v>-0.61</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" s="7" t="n">
         <v>119914</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="G4" s="7" t="n">
         <v>-28279</v>
       </c>
-      <c r="G4" t="n">
-        <v>3361</v>
-      </c>
       <c r="H4" t="n">
+        <v>-19014</v>
+      </c>
+      <c r="I4" t="n">
         <v>1700</v>
       </c>
-      <c r="I4" t="n">
-        <v>866</v>
-      </c>
       <c r="J4" t="n">
+        <v>2266</v>
+      </c>
+      <c r="K4" t="n">
         <v>44503</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>7062</v>
       </c>
-      <c r="L4" t="n">
-        <v>36064</v>
-      </c>
       <c r="M4" t="n">
+        <v>35417</v>
+      </c>
+      <c r="N4" t="n">
         <v>-3975503</v>
       </c>
-      <c r="N4" t="n">
-        <v>-0.79</v>
+      <c r="O4" t="n">
+        <v>2.72</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1249,41 +1251,46 @@
           <t>華城</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>1015</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="E6" s="6" t="n">
         <v>-2.4</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" s="6" t="n">
         <v>4703</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="6" t="n">
         <v>174</v>
       </c>
-      <c r="G6" t="n">
-        <v>799</v>
-      </c>
       <c r="H6" t="n">
+        <v>1257</v>
+      </c>
+      <c r="I6" t="n">
         <v>59</v>
       </c>
-      <c r="I6" t="n">
-        <v>-588</v>
-      </c>
       <c r="J6" t="n">
+        <v>-538</v>
+      </c>
+      <c r="K6" t="n">
         <v>157</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2739</v>
       </c>
-      <c r="L6" t="n">
-        <v>14321</v>
-      </c>
       <c r="M6" t="n">
+        <v>14121</v>
+      </c>
+      <c r="N6" t="n">
         <v>-78648</v>
       </c>
-      <c r="N6" t="n">
-        <v>21.14</v>
+      <c r="O6" t="n">
+        <v>7.49</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1355,41 +1362,46 @@
           <t>台達電</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>1255</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="E8" s="6" t="n">
         <v>-1.95</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" s="7" t="n">
         <v>13505</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="G8" s="7" t="n">
         <v>-947</v>
       </c>
-      <c r="G8" t="n">
-        <v>370</v>
-      </c>
       <c r="H8" t="n">
+        <v>-3777</v>
+      </c>
+      <c r="I8" t="n">
         <v>56</v>
       </c>
-      <c r="I8" t="n">
-        <v>1818</v>
-      </c>
       <c r="J8" t="n">
+        <v>1095</v>
+      </c>
+      <c r="K8" t="n">
         <v>475</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>6754</v>
       </c>
-      <c r="L8" t="n">
-        <v>41447</v>
-      </c>
       <c r="M8" t="n">
+        <v>39412</v>
+      </c>
+      <c r="N8" t="n">
         <v>-648590</v>
       </c>
-      <c r="N8" t="n">
-        <v>21.82</v>
+      <c r="O8" t="n">
+        <v>10.06</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1408,41 +1420,46 @@
           <t>台積電</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
         <v>1805</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="E9" s="6" t="n">
         <v>-0.82</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" s="7" t="n">
         <v>36079</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="G9" s="7" t="n">
         <v>-8629</v>
       </c>
-      <c r="G9" t="n">
-        <v>143</v>
-      </c>
       <c r="H9" t="n">
+        <v>-3136</v>
+      </c>
+      <c r="I9" t="n">
         <v>15</v>
       </c>
-      <c r="I9" t="n">
-        <v>3765</v>
-      </c>
       <c r="J9" t="n">
+        <v>3359</v>
+      </c>
+      <c r="K9" t="n">
         <v>691</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>19907</v>
       </c>
-      <c r="L9" t="n">
-        <v>101732</v>
-      </c>
       <c r="M9" t="n">
+        <v>100520</v>
+      </c>
+      <c r="N9" t="n">
         <v>-6482788</v>
       </c>
-      <c r="N9" t="n">
-        <v>23.09</v>
+      <c r="O9" t="n">
+        <v>3.62</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1514,41 +1531,46 @@
           <t>台光電</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
         <v>1790</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="E11" s="6" t="n">
         <v>-5.79</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" s="7" t="n">
         <v>4284</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="G11" s="7" t="n">
         <v>-334</v>
       </c>
-      <c r="G11" t="n">
-        <v>4787</v>
-      </c>
       <c r="H11" t="n">
+        <v>2880</v>
+      </c>
+      <c r="I11" t="n">
         <v>-440</v>
       </c>
-      <c r="I11" t="n">
-        <v>-343</v>
-      </c>
       <c r="J11" t="n">
+        <v>-704</v>
+      </c>
+      <c r="K11" t="n">
         <v>324</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>2053</v>
       </c>
-      <c r="L11" t="n">
-        <v>10459</v>
-      </c>
       <c r="M11" t="n">
+        <v>10340</v>
+      </c>
+      <c r="N11" t="n">
         <v>-89489</v>
       </c>
-      <c r="N11" t="n">
-        <v>24.4</v>
+      <c r="O11" t="n">
+        <v>7.33</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -1673,41 +1695,46 @@
           <t>光聖</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="n">
         <v>1725</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="E14" s="7" t="n">
         <v>9.869999999999999</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" s="6" t="n">
         <v>5913</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="6" t="n">
         <v>2005</v>
       </c>
-      <c r="G14" t="n">
-        <v>491</v>
-      </c>
       <c r="H14" t="n">
+        <v>2360</v>
+      </c>
+      <c r="I14" t="n">
         <v>153</v>
       </c>
-      <c r="I14" t="n">
-        <v>297</v>
-      </c>
       <c r="J14" t="n">
+        <v>398</v>
+      </c>
+      <c r="K14" t="n">
         <v>264</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>4528</v>
       </c>
-      <c r="L14" t="n">
-        <v>25675</v>
-      </c>
       <c r="M14" t="n">
+        <v>25165</v>
+      </c>
+      <c r="N14" t="n">
         <v>-19146</v>
       </c>
-      <c r="N14" t="n">
-        <v>55.09</v>
+      <c r="O14" t="n">
+        <v>26.32</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -1726,42 +1753,47 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>-2.44</v>
-      </c>
-      <c r="E15" t="n">
-        <v>905</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>2365</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>2.16</v>
       </c>
       <c r="F15" s="6" t="n">
+        <v>2182</v>
+      </c>
+      <c r="G15" s="6" t="n">
         <v>1428</v>
       </c>
-      <c r="G15" t="n">
-        <v>-1126</v>
-      </c>
       <c r="H15" t="n">
+        <v>669</v>
+      </c>
+      <c r="I15" t="n">
         <v>2</v>
       </c>
-      <c r="I15" t="n">
-        <v>1432</v>
-      </c>
       <c r="J15" t="n">
+        <v>1153</v>
+      </c>
+      <c r="K15" t="n">
         <v>-290</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>-678</v>
       </c>
-      <c r="L15" t="n">
-        <v>-36</v>
-      </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-728</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1885,42 +1917,47 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>318.5</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="E18" t="n">
-        <v>20497</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>586</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>9.94</v>
       </c>
       <c r="F18" s="6" t="n">
+        <v>32773</v>
+      </c>
+      <c r="G18" s="6" t="n">
         <v>2460</v>
       </c>
-      <c r="G18" t="n">
-        <v>-5142</v>
-      </c>
       <c r="H18" t="n">
+        <v>888</v>
+      </c>
+      <c r="I18" t="n">
         <v>2508</v>
       </c>
-      <c r="I18" t="n">
-        <v>2918</v>
-      </c>
       <c r="J18" t="n">
+        <v>5260</v>
+      </c>
+      <c r="K18" t="n">
         <v>-270</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>-971</v>
       </c>
-      <c r="L18" t="n">
-        <v>-2749</v>
-      </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-3068</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2135,41 +2172,46 @@
           <t>智邦</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>1170</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" s="6" t="n">
         <v>4811</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="6" t="n">
         <v>657</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>1465</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>-317</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>-1532</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>70</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>2661</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>13031</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>-140170</v>
       </c>
-      <c r="N23" t="n">
-        <v>-0.97</v>
+      <c r="O23" t="n">
+        <v>-1.58</v>
       </c>
     </row>
     <row r="24">
@@ -2183,42 +2225,47 @@
           <t>均華</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>962</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>826</v>
+        <v>1625</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>-6.07</v>
       </c>
       <c r="F24" s="6" t="n">
+        <v>1168</v>
+      </c>
+      <c r="G24" s="6" t="n">
         <v>96</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>307</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>0</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>62</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>12</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>-52</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>125</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2266,6 +2313,218 @@
       </c>
       <c r="N25" t="n">
         <v>8.75</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>2184</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>372</v>
+      </c>
+      <c r="H26" t="n">
+        <v>403</v>
+      </c>
+      <c r="I26" t="n">
+        <v>13</v>
+      </c>
+      <c r="J26" t="n">
+        <v>162</v>
+      </c>
+      <c r="K26" t="n">
+        <v>61</v>
+      </c>
+      <c r="L26" t="n">
+        <v>906</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4624</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-106265</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.53</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>3900</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>662</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>117</v>
+      </c>
+      <c r="H27" t="n">
+        <v>50</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-79</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-131</v>
+      </c>
+      <c r="K27" t="n">
+        <v>19</v>
+      </c>
+      <c r="L27" t="n">
+        <v>428</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1901</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-8869</v>
+      </c>
+      <c r="O27" t="n">
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>6341</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H28" t="n">
+        <v>221</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-19</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M28" t="n">
+        <v>19</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>222</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>-4.52</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>5693</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>-742</v>
+      </c>
+      <c r="H29" t="n">
+        <v>298</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-224</v>
+      </c>
+      <c r="J29" t="n">
+        <v>406</v>
+      </c>
+      <c r="K29" t="n">
+        <v>53</v>
+      </c>
+      <c r="L29" t="n">
+        <v>6371</v>
+      </c>
+      <c r="M29" t="n">
+        <v>31911</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-21489</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-2.28</v>
       </c>
     </row>
   </sheetData>
